--- a/气象/表格文件/多站记录或比较/疑难站号记录.xlsx
+++ b/气象/表格文件/多站记录或比较/疑难站号记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\多站记录或比较\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730C958A-FD3F-4547-B178-8AE8033026BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCA38A3-AF57-4460-A8CC-7C44584024C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3C3A7D5A-AFB3-47A0-AB77-2AB86F2BC01A}"/>
   </bookViews>
@@ -34,11 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>阿拉斯加</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>乌米阿特</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,8 +86,94 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>卡尔加里</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>埃德蒙顿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牧羊人湾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GSOD pogodaiklimat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>GHCND 26508
-GSOD 70162-026508 (pogodaik)</t>
+GSOD 70162-026508</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GSOD 71877</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GSOD 71123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GHCND CA002303685
+GSOD 71911</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加拿大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊卡卢伊特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NU首府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GSOD 71909
+GHCND 很多站号，但是记录量不多</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>育空堡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国际瀑布城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GSOD 70194 | 70194026413</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美国</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -533,156 +615,237 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DD9E607-FF77-43C9-A67D-1B3F05906AE5}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.59765625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="36.59765625" style="5" customWidth="1"/>
-    <col min="3" max="4" width="18.59765625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.06640625" style="1"/>
+    <col min="2" max="3" width="36.59765625" style="5" customWidth="1"/>
+    <col min="4" max="5" width="18.59765625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="6"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="6"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="6"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="6"/>
+      <c r="B4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="B8" s="9"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C8" s="9"/>
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="3"/>
+      <c r="C9" s="9"/>
       <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="3"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="3"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="3"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="3"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6"/>
       <c r="B14" s="9"/>
-      <c r="C14" s="3"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6"/>
       <c r="B15" s="9"/>
-      <c r="C15" s="3"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="3"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="6"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="3"/>
+      <c r="C17" s="9"/>
       <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="6"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="3"/>
+      <c r="C18" s="9"/>
       <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="3"/>
+      <c r="C19" s="9"/>
       <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="6"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="3"/>
+      <c r="C20" s="9"/>
       <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="6"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="3"/>
+      <c r="C21" s="9"/>
       <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/气象/表格文件/多站记录或比较/疑难站号记录.xlsx
+++ b/气象/表格文件/多站记录或比较/疑难站号记录.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\多站记录或比较\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCA38A3-AF57-4460-A8CC-7C44584024C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8D9DCD-2DE3-4689-9053-13B18E564DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3C3A7D5A-AFB3-47A0-AB77-2AB86F2BC01A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="北美专用表" sheetId="1" r:id="rId1"/>
+    <sheet name="其他地区" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>乌米阿特</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -176,12 +177,24 @@
     <t>MN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>站点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>站号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ust-Charky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +245,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -270,7 +292,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -300,6 +322,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -851,4 +879,41 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BE4BD2-0E33-4615-A38D-043C72E169C3}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="5" width="16.59765625" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="11" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/气象/表格文件/多站记录或比较/疑难站号记录.xlsx
+++ b/气象/表格文件/多站记录或比较/疑难站号记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\多站记录或比较\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8D9DCD-2DE3-4689-9053-13B18E564DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9994D786-B0F3-4ED2-A571-B60413F9EDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3C3A7D5A-AFB3-47A0-AB77-2AB86F2BC01A}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
   <si>
     <t>乌米阿特</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -187,6 +187,39 @@
   </si>
   <si>
     <t>Ust-Charky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怀特霍斯
+Whitehorse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加拿大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GSOD 71964</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YT(育空)首府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄刀镇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温尼伯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西北地区首府</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -292,7 +325,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -328,6 +361,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -785,25 +821,43 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="6"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="A9" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="6"/>
+      <c r="A10" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="E10" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="E11" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
